--- a/artfynd/A 38730-2023 artfynd.xlsx
+++ b/artfynd/A 38730-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY114"/>
+  <dimension ref="A1:AY115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12755,6 +12755,132 @@
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>112367864</v>
+      </c>
+      <c r="B115" t="n">
+        <v>97532</v>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>Flughem (Flughem), Gstr</t>
+        </is>
+      </c>
+      <c r="Q115" t="n">
+        <v>578561</v>
+      </c>
+      <c r="R115" t="n">
+        <v>6712066</v>
+      </c>
+      <c r="S115" t="n">
+        <v>15</v>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y115" t="inlineStr">
+        <is>
+          <t>2023-09-28</t>
+        </is>
+      </c>
+      <c r="Z115" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>2023-09-28</t>
+        </is>
+      </c>
+      <c r="AB115" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="AD115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT115" t="inlineStr"/>
+      <c r="AW115" t="inlineStr">
+        <is>
+          <t>Maj-Lis Koivisto</t>
+        </is>
+      </c>
+      <c r="AX115" t="inlineStr">
+        <is>
+          <t>Maj-Lis Koivisto</t>
+        </is>
+      </c>
+      <c r="AY115" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 38730-2023 artfynd.xlsx
+++ b/artfynd/A 38730-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 38730-2023 artfynd.xlsx
+++ b/artfynd/A 38730-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY115"/>
+  <dimension ref="A1:AY123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12881,6 +12881,930 @@
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>120262876</v>
+      </c>
+      <c r="B116" t="n">
+        <v>100171</v>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>Flughem, Gstr</t>
+        </is>
+      </c>
+      <c r="Q116" t="n">
+        <v>578815</v>
+      </c>
+      <c r="R116" t="n">
+        <v>6711937</v>
+      </c>
+      <c r="S116" t="n">
+        <v>10</v>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y116" t="inlineStr">
+        <is>
+          <t>2024-10-07</t>
+        </is>
+      </c>
+      <c r="Z116" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>2024-10-07</t>
+        </is>
+      </c>
+      <c r="AB116" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AD116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT116" t="inlineStr"/>
+      <c r="AW116" t="inlineStr">
+        <is>
+          <t>Angelica Pettersson</t>
+        </is>
+      </c>
+      <c r="AX116" t="inlineStr">
+        <is>
+          <t>Angelica Pettersson</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>120262434</v>
+      </c>
+      <c r="B117" t="n">
+        <v>105009</v>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>Flughem, Gstr</t>
+        </is>
+      </c>
+      <c r="Q117" t="n">
+        <v>578772</v>
+      </c>
+      <c r="R117" t="n">
+        <v>6711977</v>
+      </c>
+      <c r="S117" t="n">
+        <v>1</v>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t>2024-10-07</t>
+        </is>
+      </c>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>2024-10-07</t>
+        </is>
+      </c>
+      <c r="AB117" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
+      <c r="AD117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT117" t="inlineStr"/>
+      <c r="AW117" t="inlineStr">
+        <is>
+          <t>Angelica Pettersson</t>
+        </is>
+      </c>
+      <c r="AX117" t="inlineStr">
+        <is>
+          <t>Angelica Pettersson</t>
+        </is>
+      </c>
+      <c r="AY117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>120264038</v>
+      </c>
+      <c r="B118" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>Flughem, Gstr</t>
+        </is>
+      </c>
+      <c r="Q118" t="n">
+        <v>578733</v>
+      </c>
+      <c r="R118" t="n">
+        <v>6711959</v>
+      </c>
+      <c r="S118" t="n">
+        <v>1</v>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>2024-10-07</t>
+        </is>
+      </c>
+      <c r="Z118" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>2024-10-07</t>
+        </is>
+      </c>
+      <c r="AB118" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AD118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT118" t="inlineStr"/>
+      <c r="AW118" t="inlineStr">
+        <is>
+          <t>Katja Kleinveld</t>
+        </is>
+      </c>
+      <c r="AX118" t="inlineStr">
+        <is>
+          <t>Katja Kleinveld</t>
+        </is>
+      </c>
+      <c r="AY118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>120262582</v>
+      </c>
+      <c r="B119" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>Flughem, Gstr</t>
+        </is>
+      </c>
+      <c r="Q119" t="n">
+        <v>578772</v>
+      </c>
+      <c r="R119" t="n">
+        <v>6711977</v>
+      </c>
+      <c r="S119" t="n">
+        <v>1</v>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W119" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y119" t="inlineStr">
+        <is>
+          <t>2024-10-07</t>
+        </is>
+      </c>
+      <c r="Z119" t="inlineStr">
+        <is>
+          <t>10:59</t>
+        </is>
+      </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>2024-10-07</t>
+        </is>
+      </c>
+      <c r="AB119" t="inlineStr">
+        <is>
+          <t>10:59</t>
+        </is>
+      </c>
+      <c r="AD119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT119" t="inlineStr"/>
+      <c r="AW119" t="inlineStr">
+        <is>
+          <t>Angelica Pettersson</t>
+        </is>
+      </c>
+      <c r="AX119" t="inlineStr">
+        <is>
+          <t>Angelica Pettersson</t>
+        </is>
+      </c>
+      <c r="AY119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>120262488</v>
+      </c>
+      <c r="B120" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>Flughem, Gstr</t>
+        </is>
+      </c>
+      <c r="Q120" t="n">
+        <v>578781</v>
+      </c>
+      <c r="R120" t="n">
+        <v>6711977</v>
+      </c>
+      <c r="S120" t="n">
+        <v>1</v>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t>2024-10-07</t>
+        </is>
+      </c>
+      <c r="Z120" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>2024-10-07</t>
+        </is>
+      </c>
+      <c r="AB120" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="AD120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT120" t="inlineStr"/>
+      <c r="AW120" t="inlineStr">
+        <is>
+          <t>Katja Kleinveld</t>
+        </is>
+      </c>
+      <c r="AX120" t="inlineStr">
+        <is>
+          <t>Katja Kleinveld</t>
+        </is>
+      </c>
+      <c r="AY120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>120264387</v>
+      </c>
+      <c r="B121" t="n">
+        <v>100171</v>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>Flughem, Gstr</t>
+        </is>
+      </c>
+      <c r="Q121" t="n">
+        <v>578640</v>
+      </c>
+      <c r="R121" t="n">
+        <v>6712122</v>
+      </c>
+      <c r="S121" t="n">
+        <v>1</v>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t>2024-10-07</t>
+        </is>
+      </c>
+      <c r="Z121" t="inlineStr">
+        <is>
+          <t>12:49</t>
+        </is>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>2024-10-07</t>
+        </is>
+      </c>
+      <c r="AB121" t="inlineStr">
+        <is>
+          <t>12:49</t>
+        </is>
+      </c>
+      <c r="AD121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT121" t="inlineStr"/>
+      <c r="AW121" t="inlineStr">
+        <is>
+          <t>Katja Kleinveld</t>
+        </is>
+      </c>
+      <c r="AX121" t="inlineStr">
+        <is>
+          <t>Katja Kleinveld</t>
+        </is>
+      </c>
+      <c r="AY121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>120263754</v>
+      </c>
+      <c r="B122" t="n">
+        <v>96862</v>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>Flughem, Flughem, Gstr</t>
+        </is>
+      </c>
+      <c r="Q122" t="n">
+        <v>578761</v>
+      </c>
+      <c r="R122" t="n">
+        <v>6711853</v>
+      </c>
+      <c r="S122" t="n">
+        <v>10</v>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y122" t="inlineStr">
+        <is>
+          <t>2024-10-07</t>
+        </is>
+      </c>
+      <c r="Z122" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>2024-10-07</t>
+        </is>
+      </c>
+      <c r="AB122" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AD122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT122" t="inlineStr"/>
+      <c r="AW122" t="inlineStr">
+        <is>
+          <t>Angelica Pettersson</t>
+        </is>
+      </c>
+      <c r="AX122" t="inlineStr">
+        <is>
+          <t>Angelica Pettersson</t>
+        </is>
+      </c>
+      <c r="AY122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>120262775</v>
+      </c>
+      <c r="B123" t="n">
+        <v>105009</v>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>Flughem, Gstr</t>
+        </is>
+      </c>
+      <c r="Q123" t="n">
+        <v>578802</v>
+      </c>
+      <c r="R123" t="n">
+        <v>6711930</v>
+      </c>
+      <c r="S123" t="n">
+        <v>1</v>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W123" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y123" t="inlineStr">
+        <is>
+          <t>2024-10-07</t>
+        </is>
+      </c>
+      <c r="Z123" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>2024-10-07</t>
+        </is>
+      </c>
+      <c r="AB123" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AD123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT123" t="inlineStr"/>
+      <c r="AW123" t="inlineStr">
+        <is>
+          <t>Katja Kleinveld</t>
+        </is>
+      </c>
+      <c r="AX123" t="inlineStr">
+        <is>
+          <t>Katja Kleinveld</t>
+        </is>
+      </c>
+      <c r="AY123" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 38730-2023 artfynd.xlsx
+++ b/artfynd/A 38730-2023 artfynd.xlsx
@@ -12883,10 +12883,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>120262876</v>
+        <v>120264038</v>
       </c>
       <c r="B116" t="n">
-        <v>100171</v>
+        <v>97907</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12895,30 +12895,30 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>11</t>
         </is>
       </c>
       <c r="P116" t="inlineStr">
@@ -12927,13 +12927,13 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>578815</v>
+        <v>578733</v>
       </c>
       <c r="R116" t="n">
-        <v>6711937</v>
+        <v>6711959</v>
       </c>
       <c r="S116" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -12987,22 +12987,22 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Angelica Pettersson</t>
+          <t>Katja Kleinveld</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Angelica Pettersson</t>
+          <t>Katja Kleinveld</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>120262434</v>
+        <v>120262876</v>
       </c>
       <c r="B117" t="n">
-        <v>105009</v>
+        <v>100171</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -13015,21 +13015,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -13043,13 +13043,13 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>578772</v>
+        <v>578815</v>
       </c>
       <c r="R117" t="n">
-        <v>6711977</v>
+        <v>6711937</v>
       </c>
       <c r="S117" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -13078,7 +13078,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -13088,7 +13088,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13115,10 +13115,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>120264038</v>
+        <v>120262434</v>
       </c>
       <c r="B118" t="n">
-        <v>97907</v>
+        <v>105009</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13127,30 +13127,30 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P118" t="inlineStr">
@@ -13159,10 +13159,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>578733</v>
+        <v>578772</v>
       </c>
       <c r="R118" t="n">
-        <v>6711959</v>
+        <v>6711977</v>
       </c>
       <c r="S118" t="n">
         <v>1</v>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13204,7 +13204,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13219,12 +13219,12 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Katja Kleinveld</t>
+          <t>Angelica Pettersson</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Katja Kleinveld</t>
+          <t>Angelica Pettersson</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>

--- a/artfynd/A 38730-2023 artfynd.xlsx
+++ b/artfynd/A 38730-2023 artfynd.xlsx
@@ -12883,10 +12883,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>120264038</v>
+        <v>120262434</v>
       </c>
       <c r="B116" t="n">
-        <v>97907</v>
+        <v>105032</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12895,30 +12895,30 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P116" t="inlineStr">
@@ -12927,10 +12927,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>578733</v>
+        <v>578772</v>
       </c>
       <c r="R116" t="n">
-        <v>6711959</v>
+        <v>6711977</v>
       </c>
       <c r="S116" t="n">
         <v>1</v>
@@ -12962,7 +12962,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -12972,7 +12972,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12987,12 +12987,12 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Katja Kleinveld</t>
+          <t>Angelica Pettersson</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Katja Kleinveld</t>
+          <t>Angelica Pettersson</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
@@ -13002,7 +13002,7 @@
         <v>120262876</v>
       </c>
       <c r="B117" t="n">
-        <v>100171</v>
+        <v>100194</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -13115,10 +13115,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>120262434</v>
+        <v>120262521</v>
       </c>
       <c r="B118" t="n">
-        <v>105009</v>
+        <v>97930</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13127,30 +13127,30 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P118" t="inlineStr">
@@ -13159,7 +13159,7 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>578772</v>
+        <v>578781</v>
       </c>
       <c r="R118" t="n">
         <v>6711977</v>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13204,7 +13204,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13219,22 +13219,22 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Angelica Pettersson</t>
+          <t>Katja Kleinveld</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Angelica Pettersson</t>
+          <t>Katja Kleinveld</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>120262582</v>
+        <v>120263754</v>
       </c>
       <c r="B119" t="n">
-        <v>97907</v>
+        <v>96885</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13243,45 +13243,41 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Flughem, Gstr</t>
+          <t>Flughem, Flughem, Gstr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>578772</v>
+        <v>578761</v>
       </c>
       <c r="R119" t="n">
-        <v>6711977</v>
+        <v>6711853</v>
       </c>
       <c r="S119" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -13310,7 +13306,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13320,7 +13316,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13347,10 +13343,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>120262488</v>
+        <v>120262519</v>
       </c>
       <c r="B120" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13382,7 +13378,12 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P120" t="inlineStr">
@@ -13391,7 +13392,7 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>578781</v>
+        <v>578772</v>
       </c>
       <c r="R120" t="n">
         <v>6711977</v>
@@ -13426,7 +13427,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -13436,7 +13437,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13451,22 +13452,22 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Katja Kleinveld</t>
+          <t>Angelica Pettersson</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Katja Kleinveld</t>
+          <t>Angelica Pettersson</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>120264387</v>
+        <v>120262775</v>
       </c>
       <c r="B121" t="n">
-        <v>100171</v>
+        <v>105032</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13479,26 +13480,26 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P121" t="inlineStr">
@@ -13507,10 +13508,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>578640</v>
+        <v>578802</v>
       </c>
       <c r="R121" t="n">
-        <v>6712122</v>
+        <v>6711930</v>
       </c>
       <c r="S121" t="n">
         <v>1</v>
@@ -13542,7 +13543,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -13552,7 +13553,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13579,10 +13580,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>120263754</v>
+        <v>120264387</v>
       </c>
       <c r="B122" t="n">
-        <v>96862</v>
+        <v>100194</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13595,37 +13596,41 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Flughem, Flughem, Gstr</t>
+          <t>Flughem, Gstr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>578761</v>
+        <v>578640</v>
       </c>
       <c r="R122" t="n">
-        <v>6711853</v>
+        <v>6712122</v>
       </c>
       <c r="S122" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -13654,7 +13659,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -13664,7 +13669,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13679,22 +13684,22 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Angelica Pettersson</t>
+          <t>Katja Kleinveld</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Angelica Pettersson</t>
+          <t>Katja Kleinveld</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>120262775</v>
+        <v>120264038</v>
       </c>
       <c r="B123" t="n">
-        <v>105009</v>
+        <v>97930</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13703,30 +13708,30 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="P123" t="inlineStr">
@@ -13735,10 +13740,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>578802</v>
+        <v>578733</v>
       </c>
       <c r="R123" t="n">
-        <v>6711930</v>
+        <v>6711959</v>
       </c>
       <c r="S123" t="n">
         <v>1</v>
@@ -13770,7 +13775,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -13780,7 +13785,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD123" t="b">

--- a/artfynd/A 38730-2023 artfynd.xlsx
+++ b/artfynd/A 38730-2023 artfynd.xlsx
@@ -12883,10 +12883,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>120262434</v>
+        <v>120263754</v>
       </c>
       <c r="B116" t="n">
-        <v>105032</v>
+        <v>96885</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12899,41 +12899,37 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>221144</v>
+        <v>221945</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Flughem, Gstr</t>
+          <t>Flughem, Flughem, Gstr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>578772</v>
+        <v>578761</v>
       </c>
       <c r="R116" t="n">
-        <v>6711977</v>
+        <v>6711853</v>
       </c>
       <c r="S116" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -12962,7 +12958,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -12972,7 +12968,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12999,10 +12995,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>120262876</v>
+        <v>120262521</v>
       </c>
       <c r="B117" t="n">
-        <v>100194</v>
+        <v>97930</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -13011,30 +13007,30 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P117" t="inlineStr">
@@ -13043,13 +13039,13 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>578815</v>
+        <v>578781</v>
       </c>
       <c r="R117" t="n">
-        <v>6711937</v>
+        <v>6711977</v>
       </c>
       <c r="S117" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -13078,7 +13074,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -13088,7 +13084,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13103,19 +13099,19 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Angelica Pettersson</t>
+          <t>Katja Kleinveld</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Angelica Pettersson</t>
+          <t>Katja Kleinveld</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>120262521</v>
+        <v>120262582</v>
       </c>
       <c r="B118" t="n">
         <v>97930</v>
@@ -13150,7 +13146,7 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P118" t="inlineStr">
@@ -13159,7 +13155,7 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>578781</v>
+        <v>578772</v>
       </c>
       <c r="R118" t="n">
         <v>6711977</v>
@@ -13194,7 +13190,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13204,7 +13200,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13219,22 +13215,22 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Katja Kleinveld</t>
+          <t>Angelica Pettersson</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Katja Kleinveld</t>
+          <t>Angelica Pettersson</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>120263754</v>
+        <v>120264387</v>
       </c>
       <c r="B119" t="n">
-        <v>96885</v>
+        <v>100194</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13247,37 +13243,41 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Flughem, Flughem, Gstr</t>
+          <t>Flughem, Gstr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>578761</v>
+        <v>578640</v>
       </c>
       <c r="R119" t="n">
-        <v>6711853</v>
+        <v>6712122</v>
       </c>
       <c r="S119" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -13306,7 +13306,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13316,7 +13316,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13331,22 +13331,22 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Angelica Pettersson</t>
+          <t>Katja Kleinveld</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Angelica Pettersson</t>
+          <t>Katja Kleinveld</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>120262519</v>
+        <v>120262775</v>
       </c>
       <c r="B120" t="n">
-        <v>97930</v>
+        <v>105032</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13355,25 +13355,25 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -13381,21 +13381,16 @@
           <t>10</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P120" t="inlineStr">
         <is>
           <t>Flughem, Gstr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>578772</v>
+        <v>578802</v>
       </c>
       <c r="R120" t="n">
-        <v>6711977</v>
+        <v>6711930</v>
       </c>
       <c r="S120" t="n">
         <v>1</v>
@@ -13427,7 +13422,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -13437,7 +13432,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13452,22 +13447,22 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Angelica Pettersson</t>
+          <t>Katja Kleinveld</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Angelica Pettersson</t>
+          <t>Katja Kleinveld</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>120262775</v>
+        <v>120264038</v>
       </c>
       <c r="B121" t="n">
-        <v>105032</v>
+        <v>97930</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13476,30 +13471,30 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="P121" t="inlineStr">
@@ -13508,10 +13503,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>578802</v>
+        <v>578733</v>
       </c>
       <c r="R121" t="n">
-        <v>6711930</v>
+        <v>6711959</v>
       </c>
       <c r="S121" t="n">
         <v>1</v>
@@ -13543,7 +13538,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -13553,7 +13548,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13580,7 +13575,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>120264387</v>
+        <v>120262876</v>
       </c>
       <c r="B122" t="n">
         <v>100194</v>
@@ -13615,7 +13610,7 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P122" t="inlineStr">
@@ -13624,13 +13619,13 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>578640</v>
+        <v>578815</v>
       </c>
       <c r="R122" t="n">
-        <v>6712122</v>
+        <v>6711937</v>
       </c>
       <c r="S122" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -13659,7 +13654,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -13669,7 +13664,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13684,22 +13679,22 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Katja Kleinveld</t>
+          <t>Angelica Pettersson</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Katja Kleinveld</t>
+          <t>Angelica Pettersson</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>120264038</v>
+        <v>120262434</v>
       </c>
       <c r="B123" t="n">
-        <v>97930</v>
+        <v>105032</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13708,30 +13703,30 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P123" t="inlineStr">
@@ -13740,10 +13735,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>578733</v>
+        <v>578772</v>
       </c>
       <c r="R123" t="n">
-        <v>6711959</v>
+        <v>6711977</v>
       </c>
       <c r="S123" t="n">
         <v>1</v>
@@ -13775,7 +13770,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -13785,7 +13780,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13800,12 +13795,12 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Katja Kleinveld</t>
+          <t>Angelica Pettersson</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Katja Kleinveld</t>
+          <t>Angelica Pettersson</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>

--- a/artfynd/A 38730-2023 artfynd.xlsx
+++ b/artfynd/A 38730-2023 artfynd.xlsx
@@ -12883,10 +12883,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>120263754</v>
+        <v>120264387</v>
       </c>
       <c r="B116" t="n">
-        <v>96885</v>
+        <v>100194</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12899,37 +12899,41 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Flughem, Flughem, Gstr</t>
+          <t>Flughem, Gstr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>578761</v>
+        <v>578640</v>
       </c>
       <c r="R116" t="n">
-        <v>6711853</v>
+        <v>6712122</v>
       </c>
       <c r="S116" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -12958,7 +12962,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -12968,7 +12972,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12983,22 +12987,22 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Angelica Pettersson</t>
+          <t>Katja Kleinveld</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Angelica Pettersson</t>
+          <t>Katja Kleinveld</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>120262521</v>
+        <v>120262775</v>
       </c>
       <c r="B117" t="n">
-        <v>97930</v>
+        <v>105032</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -13007,30 +13011,30 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P117" t="inlineStr">
@@ -13039,10 +13043,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>578781</v>
+        <v>578802</v>
       </c>
       <c r="R117" t="n">
-        <v>6711977</v>
+        <v>6711930</v>
       </c>
       <c r="S117" t="n">
         <v>1</v>
@@ -13074,7 +13078,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -13084,7 +13088,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13111,10 +13115,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>120262582</v>
+        <v>120262876</v>
       </c>
       <c r="B118" t="n">
-        <v>97930</v>
+        <v>100194</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13123,30 +13127,30 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P118" t="inlineStr">
@@ -13155,13 +13159,13 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>578772</v>
+        <v>578815</v>
       </c>
       <c r="R118" t="n">
-        <v>6711977</v>
+        <v>6711937</v>
       </c>
       <c r="S118" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -13190,7 +13194,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13200,7 +13204,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13227,10 +13231,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>120264387</v>
+        <v>120262582</v>
       </c>
       <c r="B119" t="n">
-        <v>100194</v>
+        <v>97930</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13239,30 +13243,30 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P119" t="inlineStr">
@@ -13271,10 +13275,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>578640</v>
+        <v>578772</v>
       </c>
       <c r="R119" t="n">
-        <v>6712122</v>
+        <v>6711977</v>
       </c>
       <c r="S119" t="n">
         <v>1</v>
@@ -13306,7 +13310,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13316,7 +13320,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13331,22 +13335,22 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Katja Kleinveld</t>
+          <t>Angelica Pettersson</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Katja Kleinveld</t>
+          <t>Angelica Pettersson</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>120262775</v>
+        <v>120264038</v>
       </c>
       <c r="B120" t="n">
-        <v>105032</v>
+        <v>97930</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13355,30 +13359,30 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="P120" t="inlineStr">
@@ -13387,10 +13391,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>578802</v>
+        <v>578733</v>
       </c>
       <c r="R120" t="n">
-        <v>6711930</v>
+        <v>6711959</v>
       </c>
       <c r="S120" t="n">
         <v>1</v>
@@ -13422,7 +13426,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -13432,7 +13436,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13459,7 +13463,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>120264038</v>
+        <v>120262488</v>
       </c>
       <c r="B121" t="n">
         <v>97930</v>
@@ -13494,7 +13498,7 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>51</t>
         </is>
       </c>
       <c r="P121" t="inlineStr">
@@ -13503,10 +13507,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>578733</v>
+        <v>578781</v>
       </c>
       <c r="R121" t="n">
-        <v>6711959</v>
+        <v>6711977</v>
       </c>
       <c r="S121" t="n">
         <v>1</v>
@@ -13538,7 +13542,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -13548,7 +13552,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13575,10 +13579,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>120262876</v>
+        <v>120262434</v>
       </c>
       <c r="B122" t="n">
-        <v>100194</v>
+        <v>105032</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13591,21 +13595,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -13619,13 +13623,13 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>578815</v>
+        <v>578772</v>
       </c>
       <c r="R122" t="n">
-        <v>6711937</v>
+        <v>6711977</v>
       </c>
       <c r="S122" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -13654,7 +13658,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -13664,7 +13668,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13691,10 +13695,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>120262434</v>
+        <v>120263754</v>
       </c>
       <c r="B123" t="n">
-        <v>105032</v>
+        <v>96885</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13707,41 +13711,37 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>221144</v>
+        <v>221945</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Flughem, Gstr</t>
+          <t>Flughem, Flughem, Gstr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>578772</v>
+        <v>578761</v>
       </c>
       <c r="R123" t="n">
-        <v>6711977</v>
+        <v>6711853</v>
       </c>
       <c r="S123" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -13770,7 +13770,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -13780,7 +13780,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD123" t="b">

--- a/artfynd/A 38730-2023 artfynd.xlsx
+++ b/artfynd/A 38730-2023 artfynd.xlsx
@@ -12883,10 +12883,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>120264387</v>
+        <v>120262519</v>
       </c>
       <c r="B116" t="n">
-        <v>100194</v>
+        <v>97930</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12895,30 +12895,35 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P116" t="inlineStr">
@@ -12927,10 +12932,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>578640</v>
+        <v>578772</v>
       </c>
       <c r="R116" t="n">
-        <v>6712122</v>
+        <v>6711977</v>
       </c>
       <c r="S116" t="n">
         <v>1</v>
@@ -12962,7 +12967,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -12972,7 +12977,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12987,22 +12992,22 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Katja Kleinveld</t>
+          <t>Angelica Pettersson</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Katja Kleinveld</t>
+          <t>Angelica Pettersson</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>120262775</v>
+        <v>120262876</v>
       </c>
       <c r="B117" t="n">
-        <v>105032</v>
+        <v>100194</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -13015,26 +13020,26 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P117" t="inlineStr">
@@ -13043,13 +13048,13 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>578802</v>
+        <v>578815</v>
       </c>
       <c r="R117" t="n">
-        <v>6711930</v>
+        <v>6711937</v>
       </c>
       <c r="S117" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -13078,7 +13083,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -13088,7 +13093,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13103,22 +13108,22 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Katja Kleinveld</t>
+          <t>Angelica Pettersson</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Katja Kleinveld</t>
+          <t>Angelica Pettersson</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>120262876</v>
+        <v>120262775</v>
       </c>
       <c r="B118" t="n">
-        <v>100194</v>
+        <v>105032</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13131,26 +13136,26 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P118" t="inlineStr">
@@ -13159,13 +13164,13 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>578815</v>
+        <v>578802</v>
       </c>
       <c r="R118" t="n">
-        <v>6711937</v>
+        <v>6711930</v>
       </c>
       <c r="S118" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -13194,7 +13199,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13204,7 +13209,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13219,19 +13224,19 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Angelica Pettersson</t>
+          <t>Katja Kleinveld</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Angelica Pettersson</t>
+          <t>Katja Kleinveld</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>120262582</v>
+        <v>120262488</v>
       </c>
       <c r="B119" t="n">
         <v>97930</v>
@@ -13266,7 +13271,7 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>51</t>
         </is>
       </c>
       <c r="P119" t="inlineStr">
@@ -13275,7 +13280,7 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>578772</v>
+        <v>578781</v>
       </c>
       <c r="R119" t="n">
         <v>6711977</v>
@@ -13310,7 +13315,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13320,7 +13325,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13335,22 +13340,22 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Angelica Pettersson</t>
+          <t>Katja Kleinveld</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Angelica Pettersson</t>
+          <t>Katja Kleinveld</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>120264038</v>
+        <v>120262434</v>
       </c>
       <c r="B120" t="n">
-        <v>97930</v>
+        <v>105032</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13359,30 +13364,30 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P120" t="inlineStr">
@@ -13391,10 +13396,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>578733</v>
+        <v>578772</v>
       </c>
       <c r="R120" t="n">
-        <v>6711959</v>
+        <v>6711977</v>
       </c>
       <c r="S120" t="n">
         <v>1</v>
@@ -13426,7 +13431,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -13436,7 +13441,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13451,22 +13456,22 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Katja Kleinveld</t>
+          <t>Angelica Pettersson</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Katja Kleinveld</t>
+          <t>Angelica Pettersson</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>120262488</v>
+        <v>120264387</v>
       </c>
       <c r="B121" t="n">
-        <v>97930</v>
+        <v>100194</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13475,30 +13480,30 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P121" t="inlineStr">
@@ -13507,10 +13512,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>578781</v>
+        <v>578640</v>
       </c>
       <c r="R121" t="n">
-        <v>6711977</v>
+        <v>6712122</v>
       </c>
       <c r="S121" t="n">
         <v>1</v>
@@ -13542,7 +13547,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -13552,7 +13557,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13579,10 +13584,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>120262434</v>
+        <v>120264038</v>
       </c>
       <c r="B122" t="n">
-        <v>105032</v>
+        <v>97930</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13591,30 +13596,30 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>11</t>
         </is>
       </c>
       <c r="P122" t="inlineStr">
@@ -13623,10 +13628,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>578772</v>
+        <v>578733</v>
       </c>
       <c r="R122" t="n">
-        <v>6711977</v>
+        <v>6711959</v>
       </c>
       <c r="S122" t="n">
         <v>1</v>
@@ -13658,7 +13663,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -13668,7 +13673,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13683,12 +13688,12 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Angelica Pettersson</t>
+          <t>Katja Kleinveld</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Angelica Pettersson</t>
+          <t>Katja Kleinveld</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>

--- a/artfynd/A 38730-2023 artfynd.xlsx
+++ b/artfynd/A 38730-2023 artfynd.xlsx
@@ -12883,10 +12883,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>120262519</v>
+        <v>120262434</v>
       </c>
       <c r="B116" t="n">
-        <v>97930</v>
+        <v>105032</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12895,35 +12895,30 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K116" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P116" t="inlineStr">
@@ -12967,7 +12962,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -12977,7 +12972,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13004,10 +12999,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>120262876</v>
+        <v>120262582</v>
       </c>
       <c r="B117" t="n">
-        <v>100194</v>
+        <v>97930</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -13016,30 +13011,30 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P117" t="inlineStr">
@@ -13048,13 +13043,13 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>578815</v>
+        <v>578772</v>
       </c>
       <c r="R117" t="n">
-        <v>6711937</v>
+        <v>6711977</v>
       </c>
       <c r="S117" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -13083,7 +13078,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -13093,7 +13088,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13120,10 +13115,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>120262775</v>
+        <v>120262521</v>
       </c>
       <c r="B118" t="n">
-        <v>105032</v>
+        <v>97930</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13132,30 +13127,30 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P118" t="inlineStr">
@@ -13164,10 +13159,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>578802</v>
+        <v>578781</v>
       </c>
       <c r="R118" t="n">
-        <v>6711930</v>
+        <v>6711977</v>
       </c>
       <c r="S118" t="n">
         <v>1</v>
@@ -13199,7 +13194,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13209,7 +13204,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13236,10 +13231,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>120262488</v>
+        <v>120264387</v>
       </c>
       <c r="B119" t="n">
-        <v>97930</v>
+        <v>100194</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13248,30 +13243,30 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P119" t="inlineStr">
@@ -13280,10 +13275,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>578781</v>
+        <v>578640</v>
       </c>
       <c r="R119" t="n">
-        <v>6711977</v>
+        <v>6712122</v>
       </c>
       <c r="S119" t="n">
         <v>1</v>
@@ -13315,7 +13310,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13325,7 +13320,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13352,7 +13347,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>120262434</v>
+        <v>120262775</v>
       </c>
       <c r="B120" t="n">
         <v>105032</v>
@@ -13387,7 +13382,7 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P120" t="inlineStr">
@@ -13396,10 +13391,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>578772</v>
+        <v>578802</v>
       </c>
       <c r="R120" t="n">
-        <v>6711977</v>
+        <v>6711930</v>
       </c>
       <c r="S120" t="n">
         <v>1</v>
@@ -13431,7 +13426,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -13441,7 +13436,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13456,22 +13451,22 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Angelica Pettersson</t>
+          <t>Katja Kleinveld</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Angelica Pettersson</t>
+          <t>Katja Kleinveld</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>120264387</v>
+        <v>120263754</v>
       </c>
       <c r="B121" t="n">
-        <v>100194</v>
+        <v>96885</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13484,41 +13479,37 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Flughem, Gstr</t>
+          <t>Flughem, Flughem, Gstr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>578640</v>
+        <v>578761</v>
       </c>
       <c r="R121" t="n">
-        <v>6712122</v>
+        <v>6711853</v>
       </c>
       <c r="S121" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -13547,7 +13538,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -13557,7 +13548,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13572,12 +13563,12 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Katja Kleinveld</t>
+          <t>Angelica Pettersson</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Katja Kleinveld</t>
+          <t>Angelica Pettersson</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
@@ -13700,10 +13691,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>120263754</v>
+        <v>120262876</v>
       </c>
       <c r="B123" t="n">
-        <v>96885</v>
+        <v>100194</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13716,34 +13707,38 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Flughem, Flughem, Gstr</t>
+          <t>Flughem, Gstr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>578761</v>
+        <v>578815</v>
       </c>
       <c r="R123" t="n">
-        <v>6711853</v>
+        <v>6711937</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13775,7 +13770,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -13785,7 +13780,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD123" t="b">

--- a/artfynd/A 38730-2023 artfynd.xlsx
+++ b/artfynd/A 38730-2023 artfynd.xlsx
@@ -12883,10 +12883,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>120262434</v>
+        <v>120262582</v>
       </c>
       <c r="B116" t="n">
-        <v>105032</v>
+        <v>97930</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12895,30 +12895,30 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P116" t="inlineStr">
@@ -12962,7 +12962,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -12972,7 +12972,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12999,7 +12999,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>120262582</v>
+        <v>120262521</v>
       </c>
       <c r="B117" t="n">
         <v>97930</v>
@@ -13034,7 +13034,7 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P117" t="inlineStr">
@@ -13043,7 +13043,7 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>578772</v>
+        <v>578781</v>
       </c>
       <c r="R117" t="n">
         <v>6711977</v>
@@ -13078,7 +13078,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -13088,7 +13088,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13103,22 +13103,22 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Angelica Pettersson</t>
+          <t>Katja Kleinveld</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Angelica Pettersson</t>
+          <t>Katja Kleinveld</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>120262521</v>
+        <v>120263754</v>
       </c>
       <c r="B118" t="n">
-        <v>97930</v>
+        <v>96885</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13127,45 +13127,41 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Flughem, Gstr</t>
+          <t>Flughem, Flughem, Gstr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>578781</v>
+        <v>578761</v>
       </c>
       <c r="R118" t="n">
-        <v>6711977</v>
+        <v>6711853</v>
       </c>
       <c r="S118" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -13194,7 +13190,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13204,7 +13200,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13219,12 +13215,12 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Katja Kleinveld</t>
+          <t>Angelica Pettersson</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Katja Kleinveld</t>
+          <t>Angelica Pettersson</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
@@ -13347,10 +13343,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>120262775</v>
+        <v>120264038</v>
       </c>
       <c r="B120" t="n">
-        <v>105032</v>
+        <v>97930</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13359,30 +13355,30 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="P120" t="inlineStr">
@@ -13391,10 +13387,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>578802</v>
+        <v>578733</v>
       </c>
       <c r="R120" t="n">
-        <v>6711930</v>
+        <v>6711959</v>
       </c>
       <c r="S120" t="n">
         <v>1</v>
@@ -13426,7 +13422,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -13436,7 +13432,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13463,10 +13459,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>120263754</v>
+        <v>120262775</v>
       </c>
       <c r="B121" t="n">
-        <v>96885</v>
+        <v>105032</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13479,37 +13475,41 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>221945</v>
+        <v>221144</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Flughem, Flughem, Gstr</t>
+          <t>Flughem, Gstr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>578761</v>
+        <v>578802</v>
       </c>
       <c r="R121" t="n">
-        <v>6711853</v>
+        <v>6711930</v>
       </c>
       <c r="S121" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -13538,7 +13538,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -13548,7 +13548,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13563,22 +13563,22 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Angelica Pettersson</t>
+          <t>Katja Kleinveld</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Angelica Pettersson</t>
+          <t>Katja Kleinveld</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>120264038</v>
+        <v>120262876</v>
       </c>
       <c r="B122" t="n">
-        <v>97930</v>
+        <v>100194</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13587,30 +13587,30 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P122" t="inlineStr">
@@ -13619,13 +13619,13 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>578733</v>
+        <v>578815</v>
       </c>
       <c r="R122" t="n">
-        <v>6711959</v>
+        <v>6711937</v>
       </c>
       <c r="S122" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -13679,22 +13679,22 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Katja Kleinveld</t>
+          <t>Angelica Pettersson</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Katja Kleinveld</t>
+          <t>Angelica Pettersson</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>120262876</v>
+        <v>120262434</v>
       </c>
       <c r="B123" t="n">
-        <v>100194</v>
+        <v>105032</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13707,21 +13707,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -13735,13 +13735,13 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>578815</v>
+        <v>578772</v>
       </c>
       <c r="R123" t="n">
-        <v>6711937</v>
+        <v>6711977</v>
       </c>
       <c r="S123" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -13770,7 +13770,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -13780,7 +13780,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD123" t="b">

--- a/artfynd/A 38730-2023 artfynd.xlsx
+++ b/artfynd/A 38730-2023 artfynd.xlsx
@@ -12883,10 +12883,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>120262582</v>
+        <v>120262876</v>
       </c>
       <c r="B116" t="n">
-        <v>97930</v>
+        <v>100194</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12895,30 +12895,30 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P116" t="inlineStr">
@@ -12927,13 +12927,13 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>578772</v>
+        <v>578815</v>
       </c>
       <c r="R116" t="n">
-        <v>6711977</v>
+        <v>6711937</v>
       </c>
       <c r="S116" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -12962,7 +12962,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -12972,7 +12972,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12999,10 +12999,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>120262521</v>
+        <v>120262775</v>
       </c>
       <c r="B117" t="n">
-        <v>97930</v>
+        <v>105032</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -13011,30 +13011,30 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P117" t="inlineStr">
@@ -13043,10 +13043,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>578781</v>
+        <v>578802</v>
       </c>
       <c r="R117" t="n">
-        <v>6711977</v>
+        <v>6711930</v>
       </c>
       <c r="S117" t="n">
         <v>1</v>
@@ -13078,7 +13078,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -13088,7 +13088,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13115,10 +13115,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>120263754</v>
+        <v>120262434</v>
       </c>
       <c r="B118" t="n">
-        <v>96885</v>
+        <v>105032</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13131,37 +13131,41 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>221945</v>
+        <v>221144</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Flughem, Flughem, Gstr</t>
+          <t>Flughem, Gstr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>578761</v>
+        <v>578772</v>
       </c>
       <c r="R118" t="n">
-        <v>6711853</v>
+        <v>6711977</v>
       </c>
       <c r="S118" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -13190,7 +13194,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13200,7 +13204,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13227,10 +13231,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>120264387</v>
+        <v>120262488</v>
       </c>
       <c r="B119" t="n">
-        <v>100194</v>
+        <v>97930</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13239,30 +13243,30 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>51</t>
         </is>
       </c>
       <c r="P119" t="inlineStr">
@@ -13271,10 +13275,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>578640</v>
+        <v>578781</v>
       </c>
       <c r="R119" t="n">
-        <v>6712122</v>
+        <v>6711977</v>
       </c>
       <c r="S119" t="n">
         <v>1</v>
@@ -13306,7 +13310,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13316,7 +13320,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13343,10 +13347,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>120264038</v>
+        <v>120263754</v>
       </c>
       <c r="B120" t="n">
-        <v>97930</v>
+        <v>96885</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13355,45 +13359,41 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Flughem, Gstr</t>
+          <t>Flughem, Flughem, Gstr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>578733</v>
+        <v>578761</v>
       </c>
       <c r="R120" t="n">
-        <v>6711959</v>
+        <v>6711853</v>
       </c>
       <c r="S120" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -13422,7 +13422,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -13432,7 +13432,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13447,22 +13447,22 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Katja Kleinveld</t>
+          <t>Angelica Pettersson</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Katja Kleinveld</t>
+          <t>Angelica Pettersson</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>120262775</v>
+        <v>120262519</v>
       </c>
       <c r="B121" t="n">
-        <v>105032</v>
+        <v>97930</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13471,25 +13471,25 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -13497,16 +13497,21 @@
           <t>10</t>
         </is>
       </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P121" t="inlineStr">
         <is>
           <t>Flughem, Gstr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>578802</v>
+        <v>578772</v>
       </c>
       <c r="R121" t="n">
-        <v>6711930</v>
+        <v>6711977</v>
       </c>
       <c r="S121" t="n">
         <v>1</v>
@@ -13538,7 +13543,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -13548,7 +13553,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13563,22 +13568,22 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Katja Kleinveld</t>
+          <t>Angelica Pettersson</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Katja Kleinveld</t>
+          <t>Angelica Pettersson</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>120262876</v>
+        <v>120264038</v>
       </c>
       <c r="B122" t="n">
-        <v>100194</v>
+        <v>97930</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13587,30 +13592,30 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>11</t>
         </is>
       </c>
       <c r="P122" t="inlineStr">
@@ -13619,13 +13624,13 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>578815</v>
+        <v>578733</v>
       </c>
       <c r="R122" t="n">
-        <v>6711937</v>
+        <v>6711959</v>
       </c>
       <c r="S122" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -13679,22 +13684,22 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Angelica Pettersson</t>
+          <t>Katja Kleinveld</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Angelica Pettersson</t>
+          <t>Katja Kleinveld</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>120262434</v>
+        <v>120264387</v>
       </c>
       <c r="B123" t="n">
-        <v>105032</v>
+        <v>100194</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13707,26 +13712,26 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P123" t="inlineStr">
@@ -13735,10 +13740,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>578772</v>
+        <v>578640</v>
       </c>
       <c r="R123" t="n">
-        <v>6711977</v>
+        <v>6712122</v>
       </c>
       <c r="S123" t="n">
         <v>1</v>
@@ -13770,7 +13775,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -13780,7 +13785,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13795,12 +13800,12 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Angelica Pettersson</t>
+          <t>Katja Kleinveld</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Angelica Pettersson</t>
+          <t>Katja Kleinveld</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
